--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -2878,7 +2878,7 @@
         <v>121256214</v>
       </c>
       <c r="B20" t="n">
-        <v>108955</v>
+        <v>108965</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -2878,7 +2878,7 @@
         <v>121256214</v>
       </c>
       <c r="B20" t="n">
-        <v>108965</v>
+        <v>108978</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -2878,7 +2878,7 @@
         <v>121256214</v>
       </c>
       <c r="B20" t="n">
-        <v>108978</v>
+        <v>108979</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -2878,7 +2878,7 @@
         <v>121256214</v>
       </c>
       <c r="B20" t="n">
-        <v>108979</v>
+        <v>108982</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -2878,7 +2878,7 @@
         <v>121256214</v>
       </c>
       <c r="B20" t="n">
-        <v>108982</v>
+        <v>108988</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -2878,7 +2878,7 @@
         <v>121256214</v>
       </c>
       <c r="B20" t="n">
-        <v>108988</v>
+        <v>108989</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2283,7 +2283,7 @@
         <v>118374682</v>
       </c>
       <c r="B15" t="n">
-        <v>101239</v>
+        <v>101737</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>118374569</v>
       </c>
       <c r="B16" t="n">
-        <v>101239</v>
+        <v>101737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>118374233</v>
       </c>
       <c r="B17" t="n">
-        <v>101239</v>
+        <v>101737</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>118374157</v>
       </c>
       <c r="B18" t="n">
-        <v>101239</v>
+        <v>101737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>118374710</v>
       </c>
       <c r="B19" t="n">
-        <v>101239</v>
+        <v>101737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2998,6 +2998,135 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122783371</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101737</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Naddtorpetvägen (brunklöver3), Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>564529</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6626889</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>U-Sur-0816</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Även inlagda som tre separata fynd.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Einar Marklund, Lise-Lotte Norin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>118374682</v>
       </c>
       <c r="B15" t="n">
-        <v>101737</v>
+        <v>101745</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>118374569</v>
       </c>
       <c r="B16" t="n">
-        <v>101737</v>
+        <v>101745</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>118374233</v>
       </c>
       <c r="B17" t="n">
-        <v>101737</v>
+        <v>101745</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>118374157</v>
       </c>
       <c r="B18" t="n">
-        <v>101737</v>
+        <v>101745</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>118374710</v>
       </c>
       <c r="B19" t="n">
-        <v>101737</v>
+        <v>101745</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>122783371</v>
       </c>
       <c r="B21" t="n">
-        <v>101737</v>
+        <v>101745</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>118374682</v>
       </c>
       <c r="B15" t="n">
-        <v>101745</v>
+        <v>101747</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>118374569</v>
       </c>
       <c r="B16" t="n">
-        <v>101745</v>
+        <v>101747</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>118374233</v>
       </c>
       <c r="B17" t="n">
-        <v>101745</v>
+        <v>101747</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>118374157</v>
       </c>
       <c r="B18" t="n">
-        <v>101745</v>
+        <v>101747</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>118374710</v>
       </c>
       <c r="B19" t="n">
-        <v>101745</v>
+        <v>101747</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>122783371</v>
       </c>
       <c r="B21" t="n">
-        <v>101745</v>
+        <v>101747</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>118374682</v>
       </c>
       <c r="B15" t="n">
-        <v>101747</v>
+        <v>101755</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>118374569</v>
       </c>
       <c r="B16" t="n">
-        <v>101747</v>
+        <v>101755</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>118374233</v>
       </c>
       <c r="B17" t="n">
-        <v>101747</v>
+        <v>101755</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>118374157</v>
       </c>
       <c r="B18" t="n">
-        <v>101747</v>
+        <v>101755</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>118374710</v>
       </c>
       <c r="B19" t="n">
-        <v>101747</v>
+        <v>101755</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>122783371</v>
       </c>
       <c r="B21" t="n">
-        <v>101747</v>
+        <v>101755</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>118374682</v>
       </c>
       <c r="B15" t="n">
-        <v>101755</v>
+        <v>101758</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>118374569</v>
       </c>
       <c r="B16" t="n">
-        <v>101755</v>
+        <v>101758</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>118374233</v>
       </c>
       <c r="B17" t="n">
-        <v>101755</v>
+        <v>101758</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>118374157</v>
       </c>
       <c r="B18" t="n">
-        <v>101755</v>
+        <v>101758</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>118374710</v>
       </c>
       <c r="B19" t="n">
-        <v>101755</v>
+        <v>101758</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>122783371</v>
       </c>
       <c r="B21" t="n">
-        <v>101755</v>
+        <v>101758</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>118374682</v>
       </c>
       <c r="B15" t="n">
-        <v>101758</v>
+        <v>101760</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>118374569</v>
       </c>
       <c r="B16" t="n">
-        <v>101758</v>
+        <v>101760</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>118374233</v>
       </c>
       <c r="B17" t="n">
-        <v>101758</v>
+        <v>101760</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>118374157</v>
       </c>
       <c r="B18" t="n">
-        <v>101758</v>
+        <v>101760</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>118374710</v>
       </c>
       <c r="B19" t="n">
-        <v>101758</v>
+        <v>101760</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>122783371</v>
       </c>
       <c r="B21" t="n">
-        <v>101758</v>
+        <v>101760</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>118374682</v>
       </c>
       <c r="B15" t="n">
-        <v>101760</v>
+        <v>101766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>118374569</v>
       </c>
       <c r="B16" t="n">
-        <v>101760</v>
+        <v>101766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>118374233</v>
       </c>
       <c r="B17" t="n">
-        <v>101760</v>
+        <v>101766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>118374157</v>
       </c>
       <c r="B18" t="n">
-        <v>101760</v>
+        <v>101766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>118374710</v>
       </c>
       <c r="B19" t="n">
-        <v>101760</v>
+        <v>101766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>122783371</v>
       </c>
       <c r="B21" t="n">
-        <v>101760</v>
+        <v>101766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3127,6 +3127,228 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129807538</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91817</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Naddtorpsvägen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>564583</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6626772</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Gran, på snittytan, i gammal vedtrave.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129806680</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91830</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sothällen SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>564625</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6626691</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -3132,7 +3132,7 @@
         <v>129807538</v>
       </c>
       <c r="B22" t="n">
-        <v>91817</v>
+        <v>91821</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>129806680</v>
       </c>
       <c r="B23" t="n">
-        <v>91830</v>
+        <v>91834</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -3132,7 +3132,7 @@
         <v>129807538</v>
       </c>
       <c r="B22" t="n">
-        <v>91821</v>
+        <v>91823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>129806680</v>
       </c>
       <c r="B23" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -3132,7 +3132,7 @@
         <v>129807538</v>
       </c>
       <c r="B22" t="n">
-        <v>91823</v>
+        <v>91826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>129806680</v>
       </c>
       <c r="B23" t="n">
-        <v>91836</v>
+        <v>91839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -3132,7 +3132,7 @@
         <v>129807538</v>
       </c>
       <c r="B22" t="n">
-        <v>91826</v>
+        <v>91829</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>129806680</v>
       </c>
       <c r="B23" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -3132,7 +3132,7 @@
         <v>129807538</v>
       </c>
       <c r="B22" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>129806680</v>
       </c>
       <c r="B23" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -3132,7 +3132,7 @@
         <v>129807538</v>
       </c>
       <c r="B22" t="n">
-        <v>91830</v>
+        <v>91847</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>129806680</v>
       </c>
       <c r="B23" t="n">
-        <v>91843</v>
+        <v>91860</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -3132,7 +3132,7 @@
         <v>129807538</v>
       </c>
       <c r="B22" t="n">
-        <v>91863</v>
+        <v>91865</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>129806680</v>
       </c>
       <c r="B23" t="n">
-        <v>91876</v>
+        <v>91878</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54881260</v>
+        <v>67876542</v>
       </c>
       <c r="B2" t="n">
-        <v>89606</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1100</v>
+        <v>805</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosetticka</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Postia floriformis</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Jülich</t>
+          <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,17 +713,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Naddtorpet S, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564476.7302170588</v>
+        <v>564415</v>
       </c>
       <c r="R2" t="n">
-        <v>6626810.604938619</v>
+        <v>6626815</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-08-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,70 +763,72 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Kraftledningsgata</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>I gräs</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Lars Bsenko</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Lars Bsenko</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>58401513</v>
+        <v>54881260</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosetticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia floriformis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Quél.) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564594.2908212836</v>
+        <v>564477</v>
       </c>
       <c r="R3" t="n">
-        <v>6626869.058071457</v>
+        <v>6626811</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,27 +866,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-04-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-04-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
+          <t>2015-08-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,12 +886,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Liten gammelskogsrest, blandskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -938,55 +909,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>58401582</v>
+        <v>129806680</v>
       </c>
       <c r="B4" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>1101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564594.2908212836</v>
+        <v>564625</v>
       </c>
       <c r="R4" t="n">
-        <v>6626869.058071457</v>
+        <v>6626691</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,27 +977,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-04-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-04-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Höstgamla fruktkroppar på gran rötad av klibbticka</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,12 +997,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Liten gammelskogsrest, blandskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1068,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67876537</v>
+        <v>129807538</v>
       </c>
       <c r="B5" t="n">
-        <v>85301</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,37 +1031,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3739</v>
+        <v>1106</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Naddtorpet S, Vstm</t>
+          <t>Naddtorpsvägen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564492.0779614645</v>
+        <v>564583</v>
       </c>
       <c r="R5" t="n">
-        <v>6626856.70832836</v>
+        <v>6626772</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,22 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-10-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,43 +1102,39 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrskog med lövinslag</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>I mossa</t>
+          <t>Gran, på snittytan, i gammal vedtrave.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Bsenko</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Bsenko</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6850825</v>
+        <v>58401513</v>
       </c>
       <c r="B6" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,40 +1142,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221343</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Naddtorpetvägen, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564524.278512614</v>
+        <v>564594</v>
       </c>
       <c r="R6" t="n">
-        <v>6626920.229037887</v>
+        <v>6626869</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,22 +1198,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-07-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-07-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,81 +1217,79 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Liten gammelskogsrest, blandskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Einar Marklund, Lise-Lotte Norin</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>78635470</v>
+        <v>58401582</v>
       </c>
       <c r="B7" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221343</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Naddtorpetvägen, Vstm</t>
+          <t>Sothällen SV, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564530.7154152001</v>
+        <v>564594</v>
       </c>
       <c r="R7" t="n">
-        <v>6626898.177815286</v>
+        <v>6626869</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1385,22 +1313,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Höstgamla fruktkroppar på gran rötad av klibbticka</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,38 +1332,39 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Gammal grusväg i skog</t>
+          <t>Liten gammelskogsrest, blandskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>78635474</v>
+        <v>67876537</v>
       </c>
       <c r="B8" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,39 +1372,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221343</v>
+        <v>3739</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Naddtorpetvägen, Vstm</t>
+          <t>Naddtorpet S, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564568.840601029</v>
+        <v>564492</v>
       </c>
       <c r="R8" t="n">
-        <v>6626794.571195154</v>
+        <v>6626857</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1507,22 +1426,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,33 +1445,33 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Gammal grusväg i skog</t>
+          <t>Barrskog med lövinslag</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>I mossa</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Lars Bsenko</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Lars Bsenko</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>78635469</v>
+        <v>118276298</v>
       </c>
       <c r="B9" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,16 +1479,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221343</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1588,24 +1497,27 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Naddtorpetvägen, Vstm</t>
+          <t>Gamla Naddtorpsvägen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564518.5555141754</v>
+        <v>564558</v>
       </c>
       <c r="R9" t="n">
-        <v>6626930.203806936</v>
+        <v>6626842</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,22 +1541,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,38 +1555,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Gammal grusväg i skog</t>
+          <t>Vägren</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>78635473</v>
+        <v>121256214</v>
       </c>
       <c r="B10" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,16 +1590,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221343</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1710,24 +1608,27 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Naddtorpetvägen, Vstm</t>
+          <t>Gamla Naddtorpsvägen 3 (svinrot), Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564553.286841681</v>
+        <v>564558</v>
       </c>
       <c r="R10" t="n">
-        <v>6626847.694931604</v>
+        <v>6626843</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1749,24 +1650,19 @@
           <t>Ramnäs</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>U-Sur-0792</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,38 +1671,38 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Gammal grusväg i skog</t>
+          <t>vägren</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>78635472</v>
+        <v>6850825</v>
       </c>
       <c r="B11" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,24 +1728,22 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Naddtorpetvägen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564541.266256471</v>
+        <v>564524</v>
       </c>
       <c r="R11" t="n">
-        <v>6626871.66444375</v>
+        <v>6626920</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1873,22 +1767,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,7 +1786,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Gammal grusväg i skog</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1913,22 +1797,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Einar Marklund, Lise-Lotte Norin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>78635471</v>
+        <v>78635466</v>
       </c>
       <c r="B12" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564534.8903469357</v>
+        <v>564513</v>
       </c>
       <c r="R12" t="n">
-        <v>6626890.190951994</v>
+        <v>6626977</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1998,19 +1877,9 @@
           <t>2019-06-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2045,12 +1914,7 @@
         <v>78635467</v>
       </c>
       <c r="B13" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564512.1012844599</v>
+        <v>564512</v>
       </c>
       <c r="R13" t="n">
-        <v>6626953.261943649</v>
+        <v>6626953</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2120,19 +1984,9 @@
           <t>2019-06-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2164,15 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118276298</v>
+        <v>78635469</v>
       </c>
       <c r="B14" t="n">
-        <v>108714</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,16 +2029,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>221343</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2198,27 +2047,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gamla Naddtorpsvägen, Vstm</t>
+          <t>Naddtorpetvägen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564558</v>
+        <v>564519</v>
       </c>
       <c r="R14" t="n">
-        <v>6626842</v>
+        <v>6626930</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2242,12 +2088,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2256,39 +2102,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Vägren</t>
+          <t>Gammal grusväg i skog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118374682</v>
+        <v>78635470</v>
       </c>
       <c r="B15" t="n">
-        <v>101769</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2313,33 +2153,22 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Naddtorpsvägen, Vstm</t>
+          <t>Naddtorpetvägen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564509</v>
+        <v>564531</v>
       </c>
       <c r="R15" t="n">
-        <v>6626951</v>
+        <v>6626898</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2366,12 +2195,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2380,9 +2209,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Gammal grusväg i skog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2392,22 +2225,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Einar Marklund, Lise-Lotte Norin</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118374569</v>
+        <v>78635471</v>
       </c>
       <c r="B16" t="n">
-        <v>101769</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2432,33 +2260,22 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Naddtorpsvägen, Vstm</t>
+          <t>Naddtorpetvägen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564523</v>
+        <v>564535</v>
       </c>
       <c r="R16" t="n">
-        <v>6626902</v>
+        <v>6626890</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2485,12 +2302,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2499,9 +2316,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gammal grusväg i skog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2511,22 +2332,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Einar Marklund, Lise-Lotte Norin</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118374233</v>
+        <v>78635472</v>
       </c>
       <c r="B17" t="n">
-        <v>101769</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,33 +2367,22 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Naddtorpsvägen, Vstm</t>
+          <t>Naddtorpetvägen, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564529</v>
+        <v>564541</v>
       </c>
       <c r="R17" t="n">
-        <v>6626893</v>
+        <v>6626872</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2604,12 +2409,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2618,9 +2423,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal grusväg i skog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2630,22 +2439,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Einar Marklund, Lise-Lotte Norin</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118374157</v>
+        <v>78635473</v>
       </c>
       <c r="B18" t="n">
-        <v>101769</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,33 +2474,22 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Naddtorpsvägen, Vstm</t>
+          <t>Naddtorpetvägen, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564535</v>
+        <v>564553</v>
       </c>
       <c r="R18" t="n">
-        <v>6626882</v>
+        <v>6626848</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2723,12 +2516,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2737,9 +2530,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal grusväg i skog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2749,22 +2546,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Einar Marklund, Lise-Lotte Norin</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118374710</v>
+        <v>78635474</v>
       </c>
       <c r="B19" t="n">
-        <v>101769</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,33 +2581,22 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Naddtorpsvägen, Vstm</t>
+          <t>Naddtorpetvägen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564504</v>
+        <v>564569</v>
       </c>
       <c r="R19" t="n">
-        <v>6626955</v>
+        <v>6626795</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2842,12 +2623,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2856,9 +2637,13 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gammal grusväg i skog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2868,22 +2653,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Einar Marklund, Lise-Lotte Norin</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121256214</v>
+        <v>78635778</v>
       </c>
       <c r="B20" t="n">
-        <v>108989</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2891,16 +2671,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>221343</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2908,28 +2688,36 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gamla Naddtorpsvägen 3 (svinrot), Vstm</t>
+          <t>Naddtorpetvägen (brunklöver2), Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564558</v>
+        <v>564505</v>
       </c>
       <c r="R20" t="n">
-        <v>6626843</v>
+        <v>6626956</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2953,17 +2741,22 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>U-Sur-0792</t>
+          <t>U-Sur-0200</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2019-06-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 550 blommande plantor. Spridd längs vägen. Koord: 6628306/1519364/5 m; 6628359/1519349/5 m; 6628383/1519337/5 m; 6628402/1519331/5 m; 6628410/1519327/5 m; 6628442/1519315/5 m; 6628465/1519309/5 m; 6628489/1519310/5 m; 6628509/1519314/5 m; 6628653/1519295/5 m;</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2976,20 +2769,15 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>vägren</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3000,15 +2788,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122783371</v>
+        <v>118374157</v>
       </c>
       <c r="B21" t="n">
-        <v>101769</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +2818,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3043,22 +2826,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Naddtorpetvägen (brunklöver3), Vstm</t>
+          <t>Naddtorpsvägen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564529</v>
+        <v>564535</v>
       </c>
       <c r="R21" t="n">
-        <v>6626889</v>
+        <v>6626882</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3080,11 +2867,6 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>U-Sur-0816</t>
-        </is>
-      </c>
       <c r="Y21" t="inlineStr">
         <is>
           <t>2024-07-11</t>
@@ -3093,11 +2875,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Även inlagda som tre separata fynd.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3113,7 +2890,7 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -3121,45 +2898,54 @@
           <t>Einar Marklund, Lise-Lotte Norin</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129807538</v>
+        <v>118374233</v>
       </c>
       <c r="B22" t="n">
-        <v>91865</v>
+        <v>102464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1106</v>
+        <v>221343</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3167,13 +2953,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564583</v>
+        <v>564529</v>
       </c>
       <c r="R22" t="n">
-        <v>6626772</v>
+        <v>6626893</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3197,12 +2983,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3215,35 +3001,25 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Gran, på snittytan, i gammal vedtrave.</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Einar Marklund, Lise-Lotte Norin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129806680</v>
+        <v>118374569</v>
       </c>
       <c r="B23" t="n">
-        <v>91878</v>
+        <v>102464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3251,40 +3027,53 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1101</v>
+        <v>221343</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sothällen SV, Vstm</t>
+          <t>Naddtorpsvägen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564625</v>
+        <v>564523</v>
       </c>
       <c r="R23" t="n">
-        <v>6626691</v>
+        <v>6626902</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3308,12 +3097,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3326,28 +3115,484 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Einar Marklund, Lise-Lotte Norin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118374682</v>
+      </c>
+      <c r="B24" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Naddtorpsvägen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>564509</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6626951</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Einar Marklund, Lise-Lotte Norin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118374710</v>
+      </c>
+      <c r="B25" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Naddtorpsvägen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>564504</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6626955</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Einar Marklund, Lise-Lotte Norin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118374767</v>
+      </c>
+      <c r="B26" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Naddtorpsvägen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>564500</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6626961</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Einar Marklund, Lise-Lotte Norin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122783371</v>
+      </c>
+      <c r="B27" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Naddtorpetvägen (brunklöver3), Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>564529</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6626889</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>U-Sur-0816</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Även inlagda som tre separata fynd.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Einar Marklund, Lise-Lotte Norin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44798-2024 artfynd.xlsx
+++ b/artfynd/A 44798-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67876542</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54881260</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129806680</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129807538</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,6 +1268,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58401513</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1358,6 +1388,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58401582</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1465,6 +1500,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67876537</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118276298</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1694,6 +1739,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121256214</t>
         </is>
       </c>
     </row>
@@ -1801,6 +1851,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6850825</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1908,6 +1963,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635466</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2015,6 +2075,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635467</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2122,6 +2187,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635469</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2229,6 +2299,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635470</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2336,6 +2411,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635471</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2443,6 +2523,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635472</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2550,6 +2635,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635473</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2657,6 +2747,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635474</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2785,6 +2880,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635778</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2899,6 +2999,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118374157</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3013,6 +3118,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118374233</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3127,6 +3237,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118374569</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3241,6 +3356,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118374682</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3355,6 +3475,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118374710</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3469,6 +3594,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118374767</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3593,8 +3723,41 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122783371</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>